--- a/Exam/gymtrackerpro/lib/service/__tests__/it/workout-session-service/listMemberWorkoutSessions-it-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/it/workout-session-service/listMemberWorkoutSessions-it-form.xlsx
@@ -353,7 +353,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="17854612" cy="2171700"/>
+    <xdr:ext cx="17854612" cy="2857500"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">

--- a/Exam/gymtrackerpro/lib/service/__tests__/it/workout-session-service/listMemberWorkoutSessions-it-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/it/workout-session-service/listMemberWorkoutSessions-it-form.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="75">
   <si>
     <t>Statement: WorkoutSessionService.listMemberWorkoutSessions(memberId: string, options?: WorkoutSessionListOptions): Promise&lt;PageResult&lt;WorkoutSessionWithExercises&gt;&gt; — delegates to workoutSessionRepository.findAll() with memberId always injected; pagination activates only when both page and pageSize are present, switching order from date ASC to date DESC.</t>
   </si>
@@ -154,6 +154,19 @@
     <t>7</t>
   </si>
   <si>
+    <t xml:space="preserve">Two members seeded: member1 (m1@test.com), member2 (m2@test.com). Exercise seeded. Sessions seeded: member1 → "2024-01-01", member1 → "2024-06-01", member2 → "2024-06-01".
+const inputOptions: WorkoutSessionListOptions = { startDate: new Date('2024-03-01') }</t>
+  </si>
+  <si>
+    <t>service.listMemberWorkoutSessions(member1.id, inputOptions)</t>
+  </si>
+  <si>
+    <t>items = [member1's 2024-06-01 session only], total = 1 (member1's 2024-01-01 session excluded by startDate; member2's 2024-06-01 session excluded by memberId)</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
     <t xml:space="preserve">Member seeded. Exercise seeded. Five sessions seeded via workoutSessionRepository.create(): dates "2024-01-01" through "2024-05-01".
 const inputOptions: WorkoutSessionListOptions = { page: 2, pageSize: 2 }</t>
   </si>
@@ -161,7 +174,7 @@
     <t>items = [2024-03-01, 2024-02-01] (date DESC, page 2 of 3), total = 5</t>
   </si>
   <si>
-    <t>8</t>
+    <t>9</t>
   </si>
   <si>
     <t xml:space="preserve">Member seeded. Exercise seeded. Three sessions seeded: "2024-01-01", "2024-02-01", "2024-03-01".
@@ -171,7 +184,7 @@
     <t>items = [2024-03-01, 2024-02-01] (date DESC, page clamped to 1), total = 3</t>
   </si>
   <si>
-    <t>9</t>
+    <t>10</t>
   </si>
   <si>
     <t xml:space="preserve">Member seeded. Exercise seeded. Three sessions seeded: "2024-01-01", "2024-02-01", "2024-03-01".
@@ -181,7 +194,7 @@
     <t>items contains all 3 sessions (date DESC), total = 3</t>
   </si>
   <si>
-    <t>10</t>
+    <t>11</t>
   </si>
   <si>
     <t xml:space="preserve">Member seeded. Exercise seeded. Three sessions seeded: "2024-01-01", "2024-02-01", "2024-03-01".
@@ -870,7 +883,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -1042,7 +1055,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" ht="65" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -1053,10 +1066,10 @@
         <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>25</v>
@@ -1070,16 +1083,16 @@
         <v>1</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>36</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>25</v>
@@ -1093,16 +1106,16 @@
         <v>1</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>36</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>25</v>
@@ -1116,21 +1129,44 @@
         <v>1</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>36</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G11" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1159,17 +1195,17 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1181,40 +1217,40 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="M5" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1222,40 +1258,40 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C6" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
